--- a/output/pdf_financials_xlsx/REVV.xlsx
+++ b/output/pdf_financials_xlsx/REVV.xlsx
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.13002</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.593867</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.7859080000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2223,16 +2223,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.692679</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.932356</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.200261</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.834154</v>
       </c>
     </row>
     <row r="93">
@@ -4266,7 +4266,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>0.692679</v>
       </c>
@@ -10186,7 +10190,11 @@
           <t>Interest and royalty expense 18</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -10198,10 +10206,10 @@
         </is>
       </c>
       <c r="G202" s="5" t="n">
-        <v>-0.593867</v>
+        <v>0.593867</v>
       </c>
       <c r="H202" s="5" t="n">
-        <v>-0.7859080000000001</v>
+        <v>0.7859080000000001</v>
       </c>
     </row>
     <row r="203">
@@ -11384,17 +11392,21 @@
           <t>Interest and royalty expense 16</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F236" s="5" t="n">
-        <v>-0.13002</v>
+        <v>0.13002</v>
       </c>
       <c r="G236" s="5" t="n">
-        <v>-0.593867</v>
+        <v>0.593867</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/REVV.xlsx
+++ b/output/pdf_financials_xlsx/REVV.xlsx
@@ -663,10 +663,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.005834</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.06942</v>
+        <v>0.06698800000000001</v>
       </c>
     </row>
     <row r="13">
@@ -988,10 +988,10 @@
         <v>-2.342561</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.398526</v>
+        <v>3.392692</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.678746</v>
+        <v>-2.676314</v>
       </c>
     </row>
     <row r="28">
@@ -1030,10 +1030,10 @@
         <v>-2.156131</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.938613</v>
+        <v>3.932779</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.969549</v>
+        <v>-1.967117</v>
       </c>
     </row>
     <row r="30">
@@ -1051,10 +1051,10 @@
         <v>-194.3556456163566</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>58.41648625090232</v>
+        <v>58.32995787637358</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-49.44607712442127</v>
+        <v>-49.38502108592382</v>
       </c>
     </row>
     <row r="31">
@@ -1113,16 +1113,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.547352</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.611922</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.181827</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.267082</v>
       </c>
     </row>
     <row r="35">
@@ -1151,16 +1151,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.547352</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.611922</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.181827</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.267082</v>
       </c>
     </row>
     <row r="37">
@@ -1379,16 +1379,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.849803</v>
+        <v>1.302451</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.525502</v>
+        <v>0.9135799999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>7.078772</v>
+        <v>3.896945</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>12.10715</v>
+        <v>10.840068</v>
       </c>
     </row>
     <row r="49">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">

--- a/output/pdf_financials_xlsx/REVV.xlsx
+++ b/output/pdf_financials_xlsx/REVV.xlsx
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-2.342561</v>
+        <v>-2.232173</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>3.398526</v>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.110388</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0.7960159999999999</v>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.342561</v>
+        <v>-2.232173</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3.392692</v>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.156131</v>
+        <v>-2.045743</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3.932779</v>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-194.3556456163566</v>
+        <v>-184.4051690412791</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>58.32995787637358</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-4.945315618457888</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>23.42238958889824</v>
@@ -1691,16 +1691,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.274416</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.347628</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.002643</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.890042</v>
       </c>
     </row>
     <row r="65">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.062279</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.126179</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.159605</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.140529</v>
       </c>
     </row>
     <row r="68">
@@ -7516,7 +7516,11 @@
           <t>Future income tax (recovery)</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -8738,7 +8742,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -9342,7 +9350,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E178" s="5" t="n">
         <v>3.680131</v>
       </c>
@@ -11610,7 +11622,11 @@
           <t>Deferred income tax (recovery)</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
